--- a/Bangkok_CBD_Condominiums.xlsx
+++ b/Bangkok_CBD_Condominiums.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="160">
   <si>
     <t xml:space="preserve">คอนโดมิเนียม CBD กรุงเทพมหานคร 2021–2026  |  Bangkok CBD Condominium Database</t>
   </si>
@@ -122,306 +122,312 @@
     <t xml:space="preserve">Noble Development PCL</t>
   </si>
   <si>
+    <t xml:space="preserve">IAW Studio (Vitoon Kunalungkarn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCOPE Langsuan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สโคป หลังสวน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เพลินจิต / หลังสวน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.หลังสวน, ลุมพินี, ปทุมวัน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ปทุมวัน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tandem Architects (AOR) + KPF (Design Consultant) + Thomas Juul-Hansen (Interior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUNIQ Langsuan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">มิวนิค หลังสวน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.สารสิน, ลุมพินี, ปทุมวัน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Major Development PCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmer &amp; Turner (P&amp;T)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyde Heritage Thonglor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ไฮด์ เฮอริเทจ ทองหล่อ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.สุขุมวิท (ทองหล่อ), วัฒนา</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grande Asset Hotels &amp; Property + Property Perfect + Sumitomo Forestry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I WILL DESIGN STUDIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aman Residences Bangkok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">อามาน เรสซิเดนซ์ แบงค็อก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ไวร์เลส / เพลินจิต</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.วิทยุ, Nai Lert Park, ปทุมวัน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nai Lert Estate + Aman Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean-Michel Gathy (Denniston International)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Estelle Phrom Phong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เดอะ เอสเทลล์ พร้อมพงษ์</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สุขุมวิท 26, คลองเตย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">คลองเตย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raimon Land PCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCDA (Soo Chan Design Architects)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porsche Design Tower Bangkok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">พอร์ช ดีไซน์ ทาวเวอร์ แบงค็อก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">พระราม 4 / สุขุมวิท</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.พระราม 4, คลองเตย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ananda Development PCL + Porsche Design Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOM Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supalai Icon Sathorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ศุภาลัย ไอคอน สาทร</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สาทร</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.สาทร, ยานนาวา, สาทร</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supalai PCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan Architect Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life Rama 4 Asoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ไลฟ์ พระราม 4 อโศก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">อโศก / พระราม 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.พระราม 4, ควีนสิริกิต์, คลองเตย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP Thailand PCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintara MHy'ZEN Phrom Phong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ควินทาร่า มิวเซน พร้อมพงษ์</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สุขุมวิท 31, พร้อมพงษ์, วัฒนา</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintara Property Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDIN Architects Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anil Sathorn 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">อนิล สาทร 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ซ.สาทร 12, สาทร</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Unity Development Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boon Design Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOUD Residences SKV23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">คลาวด์ เรสซิเดนซ์ สุขุมวิท 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สุขุมวิท / อโศก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สุขุมวิท 23, อโศก, วัฒนา</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISLAND (Thailand) Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Silom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">แอชตัน สีลม</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สีลม</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.สีลม, บางรัก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">บางรัก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ananda Development PCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architects 49 (A49)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Residences at Sindhorn Kempinski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เดอะ เรสซิเดนซ์ แอท สินธร เคมปินสกี้</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siam Sindhorn Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Residences at Mandarin Oriental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เดอะ เรสซิเดนซ์ แอท แมนดาริน โอเรียนเต็ล</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ริมน้ำ / สีลม</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.เจริญกรุง, บางรัก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnolia Quality Development Corp. + Siam Piwat + Charoen Pokphand Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architects 49 Limited (A49)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHYTHM Ekkamai Estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ริทึ่ม เอกมัย เอสเตท</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สุขุมวิท 63 (เอกมัย), วัฒนา</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAT Architects Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUAD Silom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ควอด สีลม</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.นราธิวาสราชนครินทร์, สีลม, บางรัก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC Asset Corporation PCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casa Architect Co., Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life Sathorn Sierra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ไลฟ์ สาทร เซียร่า</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ถ.สาทร, บางรัก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Park Origin Phrom Phong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">พาร์ค ออริจิ้น พร้อมพงษ์</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สุขุมวิท 24, คลองเตย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origin Property PCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beatniq Sukhumvit 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">บีทนิค สุขุมวิท 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สุขุมวิท 32, วัฒนา</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideo Q Sukhumvit 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ไอดีโอ คิว สุขุมวิท 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สุขุมวิท 36, คลองเตย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ananda Development PCL + MBK PCL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Department of ARCHITECTURE (DBALP)</t>
   </si>
   <si>
-    <t xml:space="preserve">SCOPE Langsuan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สโคป หลังสวน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เพลินจิต / หลังสวน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.หลังสวน, ลุมพินี, ปทุมวัน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ปทุมวัน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scope Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kohn Pedersen Fox (KPF) + Thomas Juul-Hansen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUNIQ Langsuan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">มิวนิค หลังสวน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.สารสิน, ลุมพินี, ปทุมวัน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Major Development PCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architects 49 Limited (A49)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyde Heritage Thonglor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไฮด์ เฮอริเทจ ทองหล่อ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.สุขุมวิท (ทองหล่อ), วัฒนา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grande Asset Hotels &amp; Property + Property Perfect + Sumitomo Forestry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DP Architects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aman Residences Bangkok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อามาน เรสซิเดนซ์ แบงค็อก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไวร์เลส / เพลินจิต</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.วิทยุ, Nai Lert Park, ปทุมวัน</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nai Lert Estate + Aman Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jean-Michel Gathy (Denniston International)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Estelle Phrom Phong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เดอะ เอสเทลล์ พร้อมพงษ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุขุมวิท 26, คลองเตย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">คลองเตย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raimon Land PCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porsche Design Tower Bangkok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พอร์ช ดีไซน์ ทาวเวอร์ แบงค็อก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พระราม 4 / สุขุมวิท</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.พระราม 4, คลองเตย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ananda Development PCL + Porsche Design Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porsche Design Studio + Büro Ole Scheeren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supalai Icon Sathorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ศุภาลัย ไอคอน สาทร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สาทร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.สาทร, ยานนาวา, สาทร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supalai PCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan Architect Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life Rama 4 Asoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไลฟ์ พระราม 4 อโศก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อโศก / พระราม 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.พระราม 4, ควีนสิริกิต์, คลองเตย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP Thailand PCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintara MHy'ZEN Phrom Phong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ควินทาร่า มิวเซน พร้อมพงษ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุขุมวิท 31, พร้อมพงษ์, วัฒนา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintara Property Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDIN Architects Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anil Sathorn 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">อนิล สาทร 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ซ.สาทร 12, สาทร</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Unity Development Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boon Design Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLOUD Residences SKV23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">คลาวด์ เรสซิเดนซ์ สุขุมวิท 23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุขุมวิท / อโศก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุขุมวิท 23, อโศก, วัฒนา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RISLAND (Thailand) Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmer &amp; Turner (P&amp;T)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Silom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">แอชตัน สีลม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สีลม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.สีลม, บางรัก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">บางรัก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ananda Development PCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Residences at Sindhorn Kempinski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เดอะ เรสซิเดนซ์ แอท สินธร เคมปินสกี้</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siam Sindhorn Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skidmore, Owings &amp; Merrill (SOM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Residences at Mandarin Oriental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เดอะ เรสซิเดนซ์ แอท แมนดาริน โอเรียนเต็ล</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ริมน้ำ / สีลม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.เจริญกรุง, บางรัก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raimon Land PCL + Mandarin Oriental Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHYTHM Ekkamai Estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ริทึ่ม เอกมัย เอสเตท</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุขุมวิท 63 (เอกมัย), วัฒนา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAT Architects Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUAD Silom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ควอด สีลม</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.นราธิวาสราชนครินทร์, สีลม, บางรัก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC Asset Corporation PCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casa Architect Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life Sathorn Sierra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไลฟ์ สาทร เซียร่า</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ถ.สาทร, บางรัก</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Park Origin Phrom Phong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">พาร์ค ออริจิ้น พร้อมพงษ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุขุมวิท 24, คลองเตย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Origin Property PCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beatniq Sukhumvit 32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">บีทนิค สุขุมวิท 32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุขุมวิท 32, วัฒนา</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ideo Q Sukhumvit 36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ไอดีโอ คิว สุขุมวิท 36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">สุขุมวิท 36, คลองเตย</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ananda Development PCL + MBK PCL</t>
-  </si>
-  <si>
     <t xml:space="preserve">28 Chidlom</t>
   </si>
   <si>
@@ -434,7 +440,7 @@
     <t xml:space="preserve">ถ.ชิดลม, ลุมพินี, ปทุมวัน</t>
   </si>
   <si>
-    <t xml:space="preserve">Sansiri PCL</t>
+    <t xml:space="preserve">KPF + Design 103 International</t>
   </si>
   <si>
     <t xml:space="preserve">Nue Noble Ploenchit</t>
@@ -1990,7 +1996,7 @@
         <v>54</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="I9" s="13" t="n">
         <v>2021</v>
@@ -2028,25 +2034,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>2023</v>
@@ -2084,25 +2090,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E11" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="G11" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I11" s="13" t="n">
         <v>2021</v>
@@ -2140,25 +2146,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>2022</v>
@@ -2196,25 +2202,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I13" s="13" t="n">
         <v>2022</v>
@@ -2252,25 +2258,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>2021</v>
@@ -2308,25 +2314,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I15" s="13" t="n">
         <v>2022</v>
@@ -2382,7 +2388,7 @@
         <v>93</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>2019</v>
@@ -2420,10 +2426,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>29</v>
@@ -2435,10 +2441,10 @@
         <v>31</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="I17" s="13" t="n">
         <v>2021</v>
@@ -2494,7 +2500,7 @@
         <v>102</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>2021</v>
@@ -2532,25 +2538,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I19" s="13" t="n">
         <v>2022</v>
@@ -2588,25 +2594,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>90</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>92</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>2023</v>
@@ -2644,25 +2650,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>92</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I21" s="13" t="n">
         <v>2022</v>
@@ -2700,25 +2706,25 @@
         <v>19</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>2022</v>
@@ -2756,25 +2762,25 @@
         <v>20</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I23" s="13" t="n">
         <v>2021</v>
@@ -2812,25 +2818,25 @@
         <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>2022</v>
@@ -2868,25 +2874,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="I25" s="13" t="n">
         <v>2021</v>
@@ -2924,16 +2930,16 @@
         <v>23</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>31</v>
@@ -2942,7 +2948,7 @@
         <v>25</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>2022</v>
@@ -2980,25 +2986,25 @@
         <v>24</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I27" s="13" t="n">
         <v>2019</v>
@@ -3036,25 +3042,25 @@
         <v>25</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>2021</v>
@@ -3153,7 +3159,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -3161,21 +3167,21 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B3" s="19" t="n">
         <v>1</v>
@@ -3189,7 +3195,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" s="22" t="n">
         <v>1</v>
@@ -3217,7 +3223,7 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="22" t="n">
         <v>4</v>
@@ -3259,7 +3265,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>1</v>
@@ -3273,7 +3279,7 @@
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10" s="22" t="n">
         <v>1</v>
@@ -3287,7 +3293,7 @@
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B11" s="19" t="n">
         <v>1</v>
@@ -3301,7 +3307,7 @@
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B12" s="22" t="n">
         <v>1</v>
@@ -3343,7 +3349,7 @@
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B15" s="25" t="n">
         <v>25</v>
@@ -3353,12 +3359,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B19" s="28" t="n">
         <v>25</v>
@@ -3366,7 +3372,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B20" s="29" t="n">
         <v>120000</v>
@@ -3374,7 +3380,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B21" s="29" t="n">
         <v>1400000</v>
@@ -3382,7 +3388,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B22" s="28" t="n">
         <v>21</v>
@@ -3390,7 +3396,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B23" s="29" t="n">
         <v>600</v>
@@ -3398,7 +3404,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B24" s="29" t="n">
         <v>7885</v>
